--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.87488229736393</v>
+        <v>5.992168373321639</v>
       </c>
       <c r="D2" t="n">
-        <v>93.81904612653294</v>
+        <v>15.2455949955616</v>
       </c>
       <c r="E2" t="n">
-        <v>18.1223978994405</v>
+        <v>2.944889658659082</v>
       </c>
       <c r="F2" t="n">
-        <v>10.38483753118808</v>
+        <v>1.687536098818064</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.32985418685647</v>
+        <v>10.77860130536418</v>
       </c>
       <c r="D3" t="n">
-        <v>68.64120396058975</v>
+        <v>11.15419564359583</v>
       </c>
       <c r="E3" t="n">
-        <v>18.1223978994405</v>
+        <v>2.944889658659082</v>
       </c>
       <c r="F3" t="n">
-        <v>10.38483753118808</v>
+        <v>1.687536098818064</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.36344173663241</v>
+        <v>13.05905928220277</v>
       </c>
       <c r="D4" t="n">
-        <v>78.09021654626133</v>
+        <v>12.68966018876747</v>
       </c>
       <c r="E4" t="n">
-        <v>18.1223978994405</v>
+        <v>2.944889658659082</v>
       </c>
       <c r="F4" t="n">
-        <v>10.38483753118808</v>
+        <v>1.687536098818064</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
